--- a/Results_experiment/exp_4/preds_1111122222222222.xlsx
+++ b/Results_experiment/exp_4/preds_1111122222222222.xlsx
@@ -1629,7 +1629,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D2">
-        <v>2.127423763275146</v>
+        <v>2.118691921234131</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1643,7 +1643,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D3">
-        <v>2.190749645233154</v>
+        <v>3.083924531936646</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1657,7 +1657,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D4">
-        <v>2.896638870239258</v>
+        <v>3.558526515960693</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1671,7 +1671,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D5">
-        <v>4.002145290374756</v>
+        <v>3.904452323913574</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1685,7 +1685,7 @@
         <v>19.29999923706055</v>
       </c>
       <c r="D6">
-        <v>13.24049854278564</v>
+        <v>15.43653964996338</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1699,7 +1699,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D7">
-        <v>7.710554122924805</v>
+        <v>15.32357788085938</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1713,7 +1713,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D8">
-        <v>7.853308200836182</v>
+        <v>9.243284225463867</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1727,7 +1727,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D9">
-        <v>2.258383750915527</v>
+        <v>2.030997276306152</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1741,7 +1741,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D10">
-        <v>4.743490219116211</v>
+        <v>8.598919868469238</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1755,7 +1755,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D11">
-        <v>2.211774826049805</v>
+        <v>2.289831638336182</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1769,7 +1769,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D12">
-        <v>5.71137809753418</v>
+        <v>5.059072971343994</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1783,7 +1783,7 @@
         <v>0.5</v>
       </c>
       <c r="D13">
-        <v>2.225833177566528</v>
+        <v>2.141046524047852</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1797,7 +1797,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D14">
-        <v>2.211706876754761</v>
+        <v>2.107685089111328</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1811,7 +1811,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D15">
-        <v>5.804901123046875</v>
+        <v>9.926352500915527</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1825,7 +1825,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D16">
-        <v>2.151332855224609</v>
+        <v>3.108571529388428</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1839,7 +1839,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D17">
-        <v>2.138021469116211</v>
+        <v>4.805854797363281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1853,7 +1853,7 @@
         <v>10.5</v>
       </c>
       <c r="D18">
-        <v>5.810062408447266</v>
+        <v>5.772207736968994</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1867,7 +1867,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D19">
-        <v>5.089962482452393</v>
+        <v>6.425125122070312</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1881,7 +1881,7 @@
         <v>23</v>
       </c>
       <c r="D20">
-        <v>18.74624443054199</v>
+        <v>19.90957069396973</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1895,7 +1895,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D21">
-        <v>2.583900928497314</v>
+        <v>2.597947120666504</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1909,7 +1909,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D22">
-        <v>5.636360168457031</v>
+        <v>4.206098556518555</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1923,7 +1923,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>12.90328407287598</v>
+        <v>15.8850793838501</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1937,7 +1937,7 @@
         <v>9.5</v>
       </c>
       <c r="D24">
-        <v>6.17680835723877</v>
+        <v>9.162907600402832</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1951,7 +1951,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D25">
-        <v>2.128871440887451</v>
+        <v>2.779655933380127</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1965,7 +1965,7 @@
         <v>22.20000076293945</v>
       </c>
       <c r="D26">
-        <v>16.35750770568848</v>
+        <v>18.21889877319336</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1979,7 +1979,7 @@
         <v>6.5</v>
       </c>
       <c r="D27">
-        <v>2.117693901062012</v>
+        <v>2.09332537651062</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1993,7 +1993,7 @@
         <v>20.29999923706055</v>
       </c>
       <c r="D28">
-        <v>7.879786491394043</v>
+        <v>14.34763622283936</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2007,7 +2007,7 @@
         <v>15.19999980926514</v>
       </c>
       <c r="D29">
-        <v>12.43047618865967</v>
+        <v>11.3112154006958</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2021,7 +2021,7 @@
         <v>2</v>
       </c>
       <c r="D30">
-        <v>6.483300685882568</v>
+        <v>5.82866382598877</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2035,7 +2035,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D31">
-        <v>9.266781806945801</v>
+        <v>8.639043807983398</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2049,7 +2049,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D32">
-        <v>8.485265731811523</v>
+        <v>9.179097175598145</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2063,7 +2063,7 @@
         <v>26.39999961853027</v>
       </c>
       <c r="D33">
-        <v>17.08819198608398</v>
+        <v>23.09365653991699</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2077,7 +2077,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D34">
-        <v>7.434575080871582</v>
+        <v>7.598027229309082</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2091,7 +2091,7 @@
         <v>4.5</v>
       </c>
       <c r="D35">
-        <v>2.230387687683105</v>
+        <v>2.248700141906738</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2105,7 +2105,7 @@
         <v>5</v>
       </c>
       <c r="D36">
-        <v>2.831270694732666</v>
+        <v>5.069665908813477</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2119,7 +2119,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D37">
-        <v>2.105106830596924</v>
+        <v>2.087036609649658</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2133,7 +2133,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D38">
-        <v>5.148551464080811</v>
+        <v>3.994733810424805</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2147,7 +2147,7 @@
         <v>26.5</v>
       </c>
       <c r="D39">
-        <v>16.37717437744141</v>
+        <v>20.25135612487793</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2161,7 +2161,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D40">
-        <v>2.179718971252441</v>
+        <v>2.655824184417725</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2175,7 +2175,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>3.411282539367676</v>
+        <v>3.632203578948975</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2189,7 +2189,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D42">
-        <v>4.733823299407959</v>
+        <v>3.382017612457275</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2203,7 +2203,7 @@
         <v>16.70000076293945</v>
       </c>
       <c r="D43">
-        <v>12.47121334075928</v>
+        <v>17.62996864318848</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2217,7 +2217,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D44">
-        <v>6.059525966644287</v>
+        <v>7.171911239624023</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2231,7 +2231,7 @@
         <v>0.5</v>
       </c>
       <c r="D45">
-        <v>2.24805212020874</v>
+        <v>2.236255168914795</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2245,7 +2245,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D46">
-        <v>2.082358360290527</v>
+        <v>6.508634567260742</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2259,7 +2259,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D47">
-        <v>4.131472587585449</v>
+        <v>4.774656295776367</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2273,7 +2273,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D48">
-        <v>3.631044387817383</v>
+        <v>2.294806957244873</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2287,7 +2287,7 @@
         <v>9</v>
       </c>
       <c r="D49">
-        <v>6.737880706787109</v>
+        <v>9.389476776123047</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2301,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="D50">
-        <v>2.165004730224609</v>
+        <v>2.470948457717896</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2315,7 +2315,7 @@
         <v>7</v>
       </c>
       <c r="D51">
-        <v>2.160091400146484</v>
+        <v>3.474124908447266</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2329,7 +2329,7 @@
         <v>4</v>
       </c>
       <c r="D52">
-        <v>2.123641490936279</v>
+        <v>3.313904285430908</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2343,7 +2343,7 @@
         <v>4.5</v>
       </c>
       <c r="D53">
-        <v>2.169443130493164</v>
+        <v>2.350302696228027</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2357,7 +2357,7 @@
         <v>0.5</v>
       </c>
       <c r="D54">
-        <v>6.194820404052734</v>
+        <v>4.338833808898926</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2371,7 +2371,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D55">
-        <v>5.306550979614258</v>
+        <v>6.926906108856201</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2385,7 +2385,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D56">
-        <v>7.020778656005859</v>
+        <v>9.376524925231934</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2399,7 +2399,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D57">
-        <v>15.58853816986084</v>
+        <v>22.15371894836426</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2413,7 +2413,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D58">
-        <v>2.700816631317139</v>
+        <v>8.170808792114258</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2427,7 +2427,7 @@
         <v>24.20000076293945</v>
       </c>
       <c r="D59">
-        <v>13.88607215881348</v>
+        <v>14.54561996459961</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2441,7 +2441,7 @@
         <v>24.39999961853027</v>
       </c>
       <c r="D60">
-        <v>15.09565734863281</v>
+        <v>22.00517082214355</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2455,7 +2455,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D61">
-        <v>3.340977668762207</v>
+        <v>2.389693260192871</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2469,7 +2469,7 @@
         <v>0.5</v>
       </c>
       <c r="D62">
-        <v>2.132715702056885</v>
+        <v>2.513681888580322</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2483,7 +2483,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D63">
-        <v>8.097830772399902</v>
+        <v>8.691134452819824</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2497,7 +2497,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D64">
-        <v>2.130529880523682</v>
+        <v>2.683572769165039</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2511,7 +2511,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D65">
-        <v>3.272875070571899</v>
+        <v>5.167597770690918</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2525,7 +2525,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D66">
-        <v>2.803443670272827</v>
+        <v>5.413474082946777</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2539,7 +2539,7 @@
         <v>1</v>
       </c>
       <c r="D67">
-        <v>2.233885765075684</v>
+        <v>2.176150798797607</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2553,7 +2553,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D68">
-        <v>5.907553672790527</v>
+        <v>7.478442192077637</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2567,7 +2567,7 @@
         <v>4.5</v>
       </c>
       <c r="D69">
-        <v>3.319508075714111</v>
+        <v>2.548756122589111</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2581,7 +2581,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D70">
-        <v>4.029147624969482</v>
+        <v>3.648793697357178</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2595,7 +2595,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D71">
-        <v>2.072004318237305</v>
+        <v>2.045198440551758</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2609,7 +2609,7 @@
         <v>15</v>
       </c>
       <c r="D72">
-        <v>12.15493774414062</v>
+        <v>5.091286659240723</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2623,7 +2623,7 @@
         <v>8.5</v>
       </c>
       <c r="D73">
-        <v>7.97441577911377</v>
+        <v>14.78942108154297</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2637,7 +2637,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D74">
-        <v>3.998555660247803</v>
+        <v>6.52076244354248</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2651,7 +2651,7 @@
         <v>16.60000038146973</v>
       </c>
       <c r="D75">
-        <v>8.620741844177246</v>
+        <v>5.419146537780762</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2665,7 +2665,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D76">
-        <v>2.13569164276123</v>
+        <v>2.398764848709106</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2679,7 +2679,7 @@
         <v>13.19999980926514</v>
       </c>
       <c r="D77">
-        <v>3.578837394714355</v>
+        <v>4.487648487091064</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2693,7 +2693,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D78">
-        <v>2.095947980880737</v>
+        <v>2.33540153503418</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2707,7 +2707,7 @@
         <v>1</v>
       </c>
       <c r="D79">
-        <v>2.143525123596191</v>
+        <v>2.099560737609863</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2721,7 +2721,7 @@
         <v>8.5</v>
       </c>
       <c r="D80">
-        <v>5.06861400604248</v>
+        <v>5.627346992492676</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2735,7 +2735,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D81">
-        <v>4.71235179901123</v>
+        <v>4.263724803924561</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2749,7 +2749,7 @@
         <v>4</v>
       </c>
       <c r="D82">
-        <v>5.317624568939209</v>
+        <v>5.465031147003174</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2763,7 +2763,7 @@
         <v>34.79999923706055</v>
       </c>
       <c r="D83">
-        <v>8.554736137390137</v>
+        <v>16.08761787414551</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2777,7 +2777,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D84">
-        <v>2.116302490234375</v>
+        <v>2.207272052764893</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2791,7 +2791,7 @@
         <v>29</v>
       </c>
       <c r="D85">
-        <v>4.638144969940186</v>
+        <v>3.599973678588867</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2805,7 +2805,7 @@
         <v>15.10000038146973</v>
       </c>
       <c r="D86">
-        <v>2.200797557830811</v>
+        <v>2.903867244720459</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2819,7 +2819,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D87">
-        <v>2.160841941833496</v>
+        <v>2.12721061706543</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2833,7 +2833,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D88">
-        <v>9.093957901000977</v>
+        <v>12.89552974700928</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2847,7 +2847,7 @@
         <v>12.30000019073486</v>
       </c>
       <c r="D89">
-        <v>13.41429138183594</v>
+        <v>14.72073268890381</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2861,7 +2861,7 @@
         <v>9</v>
       </c>
       <c r="D90">
-        <v>2.771645069122314</v>
+        <v>6.63156795501709</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2875,7 +2875,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D91">
-        <v>6.211808204650879</v>
+        <v>9.628469467163086</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2889,7 +2889,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D92">
-        <v>2.139263391494751</v>
+        <v>2.374825954437256</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2903,7 +2903,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D93">
-        <v>4.728719234466553</v>
+        <v>8.703310012817383</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2917,7 +2917,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D94">
-        <v>2.413491725921631</v>
+        <v>2.412399768829346</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2931,7 +2931,7 @@
         <v>2</v>
       </c>
       <c r="D95">
-        <v>2.118893146514893</v>
+        <v>2.827476501464844</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2945,7 +2945,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D96">
-        <v>2.176267623901367</v>
+        <v>2.243056774139404</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2959,7 +2959,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D97">
-        <v>2.076989889144897</v>
+        <v>2.186540603637695</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2973,7 +2973,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D98">
-        <v>2.576633930206299</v>
+        <v>6.840576648712158</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2987,7 +2987,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D99">
-        <v>2.214205026626587</v>
+        <v>2.074635744094849</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3001,7 +3001,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D100">
-        <v>2.17038631439209</v>
+        <v>2.114384651184082</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3015,7 +3015,7 @@
         <v>4</v>
       </c>
       <c r="D101">
-        <v>4.329461097717285</v>
+        <v>3.363681316375732</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3029,7 +3029,7 @@
         <v>5.5</v>
       </c>
       <c r="D102">
-        <v>2.163454055786133</v>
+        <v>4.485718727111816</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3043,7 +3043,7 @@
         <v>19.5</v>
       </c>
       <c r="D103">
-        <v>4.100034236907959</v>
+        <v>8.257948875427246</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3057,7 +3057,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D104">
-        <v>2.09989070892334</v>
+        <v>5.720940589904785</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3071,7 +3071,7 @@
         <v>21.5</v>
       </c>
       <c r="D105">
-        <v>15.7410831451416</v>
+        <v>18.33304786682129</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3085,7 +3085,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D106">
-        <v>2.146215915679932</v>
+        <v>2.533194541931152</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3099,7 +3099,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D107">
-        <v>5.922473430633545</v>
+        <v>5.77818489074707</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3113,7 +3113,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D108">
-        <v>2.169694423675537</v>
+        <v>2.210269451141357</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3127,7 +3127,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D109">
-        <v>2.130800247192383</v>
+        <v>2.274580478668213</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3141,7 +3141,7 @@
         <v>10.5</v>
       </c>
       <c r="D110">
-        <v>5.16662073135376</v>
+        <v>6.218700408935547</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3155,7 +3155,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D111">
-        <v>3.185462951660156</v>
+        <v>3.776832103729248</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3169,7 +3169,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D112">
-        <v>5.375811100006104</v>
+        <v>6.480062484741211</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3183,7 +3183,7 @@
         <v>18.5</v>
       </c>
       <c r="D113">
-        <v>7.282297611236572</v>
+        <v>9.773444175720215</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3197,7 +3197,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D114">
-        <v>21.73850631713867</v>
+        <v>24.94756889343262</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3211,7 +3211,7 @@
         <v>32.09999847412109</v>
       </c>
       <c r="D115">
-        <v>15.99538993835449</v>
+        <v>19.91136741638184</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3225,7 +3225,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D116">
-        <v>2.090780258178711</v>
+        <v>5.046319484710693</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3239,7 +3239,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D117">
-        <v>4.910081386566162</v>
+        <v>9.778626441955566</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3253,7 +3253,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D118">
-        <v>2.11432409286499</v>
+        <v>2.417194128036499</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3267,7 +3267,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D119">
-        <v>2.402318000793457</v>
+        <v>3.116715908050537</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3281,7 +3281,7 @@
         <v>43.59999847412109</v>
       </c>
       <c r="D120">
-        <v>25.75812530517578</v>
+        <v>31.7754077911377</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3295,7 +3295,7 @@
         <v>21.29999923706055</v>
       </c>
       <c r="D121">
-        <v>23.76067161560059</v>
+        <v>26.70300483703613</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3309,7 +3309,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D122">
-        <v>2.208320140838623</v>
+        <v>2.44034481048584</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3323,7 +3323,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D123">
-        <v>5.657276153564453</v>
+        <v>6.197527408599854</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3337,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="D124">
-        <v>3.395044803619385</v>
+        <v>3.172528266906738</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3351,7 +3351,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D125">
-        <v>2.09796142578125</v>
+        <v>2.525979280471802</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3365,7 +3365,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D126">
-        <v>7.496164798736572</v>
+        <v>10.26548862457275</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3379,7 +3379,7 @@
         <v>17.10000038146973</v>
       </c>
       <c r="D127">
-        <v>6.485807418823242</v>
+        <v>9.275277137756348</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3393,7 +3393,7 @@
         <v>8</v>
       </c>
       <c r="D128">
-        <v>2.971341609954834</v>
+        <v>4.992482662200928</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3407,7 +3407,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D129">
-        <v>2.235188484191895</v>
+        <v>2.198519706726074</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3421,7 +3421,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D130">
-        <v>4.863475322723389</v>
+        <v>4.638309955596924</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3435,7 +3435,7 @@
         <v>2</v>
       </c>
       <c r="D131">
-        <v>2.181936025619507</v>
+        <v>3.104176998138428</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3449,7 +3449,7 @@
         <v>1</v>
       </c>
       <c r="D132">
-        <v>4.447847366333008</v>
+        <v>3.050445556640625</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3463,7 +3463,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D133">
-        <v>2.182477235794067</v>
+        <v>2.593937873840332</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3477,7 +3477,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D134">
-        <v>2.156760215759277</v>
+        <v>2.548471450805664</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3491,7 +3491,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D135">
-        <v>2.174965858459473</v>
+        <v>2.579507112503052</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3505,7 +3505,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D136">
-        <v>2.207431316375732</v>
+        <v>2.031389713287354</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3519,7 +3519,7 @@
         <v>12.30000019073486</v>
       </c>
       <c r="D137">
-        <v>9.101720809936523</v>
+        <v>12.17719745635986</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3533,7 +3533,7 @@
         <v>3.5</v>
       </c>
       <c r="D138">
-        <v>2.214414119720459</v>
+        <v>2.444527864456177</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3547,7 +3547,7 @@
         <v>8</v>
       </c>
       <c r="D139">
-        <v>5.883471488952637</v>
+        <v>6.938951015472412</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3561,7 +3561,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D140">
-        <v>2.22258734703064</v>
+        <v>2.068373203277588</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3575,7 +3575,7 @@
         <v>28.70000076293945</v>
       </c>
       <c r="D141">
-        <v>16.88815498352051</v>
+        <v>18.91837501525879</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3589,7 +3589,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D142">
-        <v>6.494392395019531</v>
+        <v>6.087594032287598</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3603,7 +3603,7 @@
         <v>10.69999980926514</v>
       </c>
       <c r="D143">
-        <v>3.441761493682861</v>
+        <v>5.589400291442871</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3617,7 +3617,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D144">
-        <v>4.259341716766357</v>
+        <v>3.879474639892578</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3631,7 +3631,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D145">
-        <v>6.170717239379883</v>
+        <v>5.168703556060791</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3645,7 +3645,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D146">
-        <v>5.071857452392578</v>
+        <v>2.844503879547119</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3659,7 +3659,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D147">
-        <v>3.243687152862549</v>
+        <v>5.137443542480469</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3673,7 +3673,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D148">
-        <v>2.195607662200928</v>
+        <v>2.456292629241943</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3687,7 +3687,7 @@
         <v>13.19999980926514</v>
       </c>
       <c r="D149">
-        <v>6.959569454193115</v>
+        <v>8.060017585754395</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3701,7 +3701,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D150">
-        <v>4.577728748321533</v>
+        <v>4.746635913848877</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3715,7 +3715,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D151">
-        <v>6.128918170928955</v>
+        <v>5.995500564575195</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3729,7 +3729,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D152">
-        <v>8.301307678222656</v>
+        <v>7.773944854736328</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3743,7 +3743,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D153">
-        <v>5.658535957336426</v>
+        <v>4.511703968048096</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3757,7 +3757,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D154">
-        <v>5.70362377166748</v>
+        <v>3.462266445159912</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3771,7 +3771,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D155">
-        <v>2.19709038734436</v>
+        <v>2.265011310577393</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>2.216651916503906</v>
+        <v>2.333980321884155</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3799,7 +3799,7 @@
         <v>26.29999923706055</v>
       </c>
       <c r="D157">
-        <v>19.30459403991699</v>
+        <v>9.561100959777832</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3813,7 +3813,7 @@
         <v>16</v>
       </c>
       <c r="D158">
-        <v>4.74381160736084</v>
+        <v>7.467583656311035</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3827,7 +3827,7 @@
         <v>0.5</v>
       </c>
       <c r="D159">
-        <v>4.508265018463135</v>
+        <v>2.340030670166016</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3841,7 +3841,7 @@
         <v>27.79999923706055</v>
       </c>
       <c r="D160">
-        <v>14.98525238037109</v>
+        <v>14.71946239471436</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3855,7 +3855,7 @@
         <v>41.79999923706055</v>
       </c>
       <c r="D161">
-        <v>16.30967712402344</v>
+        <v>23.75944519042969</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3869,7 +3869,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D162">
-        <v>4.652765274047852</v>
+        <v>5.422322750091553</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3883,7 +3883,7 @@
         <v>0.5</v>
       </c>
       <c r="D163">
-        <v>2.206693172454834</v>
+        <v>2.027281761169434</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3897,7 +3897,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="D164">
-        <v>6.817016124725342</v>
+        <v>8.532198905944824</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3911,7 +3911,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D165">
-        <v>5.892698764801025</v>
+        <v>2.279759407043457</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3925,7 +3925,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D166">
-        <v>4.112141132354736</v>
+        <v>3.041896820068359</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3939,7 +3939,7 @@
         <v>5</v>
       </c>
       <c r="D167">
-        <v>3.803051948547363</v>
+        <v>4.075498104095459</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3953,7 +3953,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D168">
-        <v>2.104881763458252</v>
+        <v>4.691598892211914</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3967,7 +3967,7 @@
         <v>10.30000019073486</v>
       </c>
       <c r="D169">
-        <v>9.379743576049805</v>
+        <v>10.57638454437256</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3981,7 +3981,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D170">
-        <v>2.432405948638916</v>
+        <v>7.200220108032227</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3995,7 +3995,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D171">
-        <v>7.572219371795654</v>
+        <v>7.984315872192383</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4009,7 +4009,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D172">
-        <v>4.255283832550049</v>
+        <v>2.381392478942871</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4023,7 +4023,7 @@
         <v>18.20000076293945</v>
       </c>
       <c r="D173">
-        <v>12.70679187774658</v>
+        <v>21.31470680236816</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4037,7 +4037,7 @@
         <v>3</v>
       </c>
       <c r="D174">
-        <v>2.135665893554688</v>
+        <v>2.721640110015869</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4051,7 +4051,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D175">
-        <v>2.220502853393555</v>
+        <v>2.336639404296875</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4065,7 +4065,7 @@
         <v>14</v>
       </c>
       <c r="D176">
-        <v>6.913189888000488</v>
+        <v>10.05059432983398</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4079,7 +4079,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D177">
-        <v>3.342901706695557</v>
+        <v>2.686162948608398</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4093,7 +4093,7 @@
         <v>12.10000038146973</v>
       </c>
       <c r="D178">
-        <v>10.00463676452637</v>
+        <v>10.02501487731934</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4107,7 +4107,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D179">
-        <v>7.87653636932373</v>
+        <v>5.465229988098145</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4121,7 +4121,7 @@
         <v>18.79999923706055</v>
       </c>
       <c r="D180">
-        <v>11.42394256591797</v>
+        <v>13.35642719268799</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4135,7 +4135,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D181">
-        <v>2.047890186309814</v>
+        <v>2.395534515380859</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4149,7 +4149,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D182">
-        <v>2.240108251571655</v>
+        <v>2.00203275680542</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4163,7 +4163,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D183">
-        <v>4.417677402496338</v>
+        <v>5.876626968383789</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4177,7 +4177,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D184">
-        <v>6.107739448547363</v>
+        <v>11.31797981262207</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4191,7 +4191,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D185">
-        <v>2.191399097442627</v>
+        <v>3.143836498260498</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4205,7 +4205,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D186">
-        <v>3.383777618408203</v>
+        <v>5.120792388916016</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4219,7 +4219,7 @@
         <v>13.80000019073486</v>
       </c>
       <c r="D187">
-        <v>8.068543434143066</v>
+        <v>12.62492847442627</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4233,7 +4233,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D188">
-        <v>2.182808399200439</v>
+        <v>2.096061706542969</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4247,7 +4247,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D189">
-        <v>2.184562683105469</v>
+        <v>2.523238658905029</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4261,7 +4261,7 @@
         <v>5.5</v>
       </c>
       <c r="D190">
-        <v>2.109663486480713</v>
+        <v>2.276078701019287</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4275,7 +4275,7 @@
         <v>10.10000038146973</v>
       </c>
       <c r="D191">
-        <v>9.397826194763184</v>
+        <v>8.147983551025391</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4289,7 +4289,7 @@
         <v>2</v>
       </c>
       <c r="D192">
-        <v>2.191297054290771</v>
+        <v>2.353508472442627</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4303,7 +4303,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D193">
-        <v>3.142129898071289</v>
+        <v>5.535378932952881</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4317,7 +4317,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D194">
-        <v>2.468084335327148</v>
+        <v>2.477358818054199</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4331,7 +4331,7 @@
         <v>0.5</v>
       </c>
       <c r="D195">
-        <v>2.07639741897583</v>
+        <v>2.20911693572998</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4345,7 +4345,7 @@
         <v>32.59999847412109</v>
       </c>
       <c r="D196">
-        <v>22.70326232910156</v>
+        <v>25.74406814575195</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4359,7 +4359,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D197">
-        <v>11.59213638305664</v>
+        <v>4.674478530883789</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4373,7 +4373,7 @@
         <v>22.89999961853027</v>
       </c>
       <c r="D198">
-        <v>5.900738716125488</v>
+        <v>14.95436191558838</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4387,7 +4387,7 @@
         <v>20.89999961853027</v>
       </c>
       <c r="D199">
-        <v>14.87898349761963</v>
+        <v>17.46671104431152</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4401,7 +4401,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D200">
-        <v>2.184888362884521</v>
+        <v>2.306493997573853</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4415,7 +4415,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D201">
-        <v>2.074277400970459</v>
+        <v>2.96611213684082</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4429,7 +4429,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D202">
-        <v>2.193328380584717</v>
+        <v>2.615815162658691</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4443,7 +4443,7 @@
         <v>4.5</v>
       </c>
       <c r="D203">
-        <v>3.190762042999268</v>
+        <v>4.426610946655273</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4457,7 +4457,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D204">
-        <v>9.492483139038086</v>
+        <v>11.28092670440674</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4471,7 +4471,7 @@
         <v>2.5</v>
       </c>
       <c r="D205">
-        <v>2.194613218307495</v>
+        <v>2.346776485443115</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4485,7 +4485,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D206">
-        <v>4.842337131500244</v>
+        <v>3.039235591888428</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4499,7 +4499,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D207">
-        <v>6.149683475494385</v>
+        <v>10.48595905303955</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4513,7 +4513,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D208">
-        <v>3.048005342483521</v>
+        <v>6.209716796875</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4527,7 +4527,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D209">
-        <v>3.174550294876099</v>
+        <v>5.259775638580322</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4541,7 +4541,7 @@
         <v>4</v>
       </c>
       <c r="D210">
-        <v>6.329107284545898</v>
+        <v>7.742060661315918</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4555,7 +4555,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D211">
-        <v>2.560186862945557</v>
+        <v>3.936841011047363</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4569,7 +4569,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D212">
-        <v>5.255408763885498</v>
+        <v>4.811986446380615</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4583,7 +4583,7 @@
         <v>6</v>
       </c>
       <c r="D213">
-        <v>2.218872547149658</v>
+        <v>4.669715881347656</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4597,7 +4597,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D214">
-        <v>5.809359550476074</v>
+        <v>5.130978107452393</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4611,7 +4611,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D215">
-        <v>3.016124486923218</v>
+        <v>5.586159229278564</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4625,7 +4625,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D216">
-        <v>4.048403263092041</v>
+        <v>3.141275882720947</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4639,7 +4639,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D217">
-        <v>2.076268196105957</v>
+        <v>4.022509574890137</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4653,7 +4653,7 @@
         <v>5.5</v>
       </c>
       <c r="D218">
-        <v>2.114618301391602</v>
+        <v>6.897234439849854</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4667,7 +4667,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D219">
-        <v>2.22783374786377</v>
+        <v>2.293628215789795</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4681,7 +4681,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D220">
-        <v>2.198509931564331</v>
+        <v>2.568895101547241</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4695,7 +4695,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D221">
-        <v>2.192886829376221</v>
+        <v>2.131434202194214</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4709,7 +4709,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D222">
-        <v>10.38615417480469</v>
+        <v>9.650869369506836</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4723,7 +4723,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D223">
-        <v>4.516134738922119</v>
+        <v>4.833183288574219</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4737,7 +4737,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D224">
-        <v>2.07847785949707</v>
+        <v>2.204007625579834</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4751,7 +4751,7 @@
         <v>25.79999923706055</v>
       </c>
       <c r="D225">
-        <v>12.32074356079102</v>
+        <v>17.88913917541504</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4765,7 +4765,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D226">
-        <v>5.608826637268066</v>
+        <v>5.552028656005859</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4779,7 +4779,7 @@
         <v>12</v>
       </c>
       <c r="D227">
-        <v>4.332212448120117</v>
+        <v>4.786076068878174</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4793,7 +4793,7 @@
         <v>26.60000038146973</v>
       </c>
       <c r="D228">
-        <v>12.63502216339111</v>
+        <v>20.26379776000977</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4807,7 +4807,7 @@
         <v>17.70000076293945</v>
       </c>
       <c r="D229">
-        <v>13.91351509094238</v>
+        <v>13.68443012237549</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4821,7 +4821,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D230">
-        <v>6.705657482147217</v>
+        <v>6.649467945098877</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4835,7 +4835,7 @@
         <v>18.5</v>
       </c>
       <c r="D231">
-        <v>15.21157264709473</v>
+        <v>18.32377433776855</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4849,7 +4849,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D232">
-        <v>2.165454864501953</v>
+        <v>2.158298015594482</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4863,7 +4863,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D233">
-        <v>2.191439390182495</v>
+        <v>2.155552387237549</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4877,7 +4877,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D234">
-        <v>2.131565570831299</v>
+        <v>2.1392502784729</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4891,7 +4891,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D235">
-        <v>2.234139442443848</v>
+        <v>2.233091115951538</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4905,7 +4905,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D236">
-        <v>2.85718297958374</v>
+        <v>4.55097770690918</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4919,7 +4919,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D237">
-        <v>5.446235656738281</v>
+        <v>14.32368564605713</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4933,7 +4933,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D238">
-        <v>2.208245754241943</v>
+        <v>2.315365314483643</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4947,7 +4947,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D239">
-        <v>5.097385406494141</v>
+        <v>9.795731544494629</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4961,7 +4961,7 @@
         <v>5.5</v>
       </c>
       <c r="D240">
-        <v>2.106794357299805</v>
+        <v>6.067173957824707</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4975,7 +4975,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D241">
-        <v>4.050745487213135</v>
+        <v>5.378626823425293</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4989,7 +4989,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D242">
-        <v>2.102429151535034</v>
+        <v>2.46738600730896</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5003,7 +5003,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D243">
-        <v>2.151517391204834</v>
+        <v>2.428074836730957</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5017,7 +5017,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D244">
-        <v>2.150425434112549</v>
+        <v>2.550510883331299</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5031,7 +5031,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D245">
-        <v>2.593641757965088</v>
+        <v>2.948078155517578</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5045,7 +5045,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D246">
-        <v>4.543833255767822</v>
+        <v>5.23377513885498</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5059,7 +5059,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D247">
-        <v>2.127800226211548</v>
+        <v>2.348498821258545</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5073,7 +5073,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D248">
-        <v>4.514626026153564</v>
+        <v>9.061588287353516</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5087,7 +5087,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D249">
-        <v>2.925814151763916</v>
+        <v>3.726486206054688</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5101,7 +5101,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D250">
-        <v>2.084388494491577</v>
+        <v>2.422977924346924</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5115,7 +5115,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D251">
-        <v>5.582832813262939</v>
+        <v>8.647951126098633</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5129,7 +5129,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D252">
-        <v>2.07708215713501</v>
+        <v>2.217270851135254</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5143,7 +5143,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D253">
-        <v>2.844418525695801</v>
+        <v>2.669896602630615</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5157,7 +5157,7 @@
         <v>12.10000038146973</v>
       </c>
       <c r="D254">
-        <v>7.00734281539917</v>
+        <v>11.59750366210938</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5171,7 +5171,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D255">
-        <v>4.997604846954346</v>
+        <v>4.300372123718262</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5185,7 +5185,7 @@
         <v>7.5</v>
       </c>
       <c r="D256">
-        <v>4.663228511810303</v>
+        <v>4.958412647247314</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -5199,7 +5199,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D257">
-        <v>2.211591005325317</v>
+        <v>2.171268463134766</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -5213,7 +5213,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D258">
-        <v>2.100708723068237</v>
+        <v>2.556031703948975</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -5227,7 +5227,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D259">
-        <v>2.097445011138916</v>
+        <v>3.494081020355225</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -5241,7 +5241,7 @@
         <v>7</v>
       </c>
       <c r="D260">
-        <v>5.036187171936035</v>
+        <v>2.887363910675049</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -5255,7 +5255,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D261">
-        <v>9.740091323852539</v>
+        <v>10.83736705780029</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -5269,7 +5269,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D262">
-        <v>2.177833795547485</v>
+        <v>5.126670360565186</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -5283,7 +5283,7 @@
         <v>3.5</v>
       </c>
       <c r="D263">
-        <v>3.375551700592041</v>
+        <v>2.528974056243896</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -5297,7 +5297,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D264">
-        <v>3.197601318359375</v>
+        <v>2.052721500396729</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -5311,7 +5311,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D265">
-        <v>11.9559154510498</v>
+        <v>18.43274879455566</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -5325,7 +5325,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D266">
-        <v>2.116180419921875</v>
+        <v>2.133293628692627</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5339,7 +5339,7 @@
         <v>14</v>
       </c>
       <c r="D267">
-        <v>4.940492630004883</v>
+        <v>7.126999855041504</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5353,7 +5353,7 @@
         <v>3.5</v>
       </c>
       <c r="D268">
-        <v>3.069783210754395</v>
+        <v>2.807454586029053</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -5367,7 +5367,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D269">
-        <v>6.216640472412109</v>
+        <v>8.16486644744873</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -5381,7 +5381,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D270">
-        <v>2.351908683776855</v>
+        <v>3.72798490524292</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5395,7 +5395,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D271">
-        <v>3.079380035400391</v>
+        <v>2.635055065155029</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5409,7 +5409,7 @@
         <v>22.29999923706055</v>
       </c>
       <c r="D272">
-        <v>13.63752937316895</v>
+        <v>15.43232536315918</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5423,7 +5423,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D273">
-        <v>6.421283721923828</v>
+        <v>5.558818817138672</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5437,7 +5437,7 @@
         <v>13.19999980926514</v>
       </c>
       <c r="D274">
-        <v>10.22765159606934</v>
+        <v>15.41166210174561</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5451,7 +5451,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D275">
-        <v>4.275903701782227</v>
+        <v>4.123250484466553</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5465,7 +5465,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D276">
-        <v>2.140771389007568</v>
+        <v>4.689605712890625</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5479,7 +5479,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D277">
-        <v>3.964536190032959</v>
+        <v>5.102285861968994</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5493,7 +5493,7 @@
         <v>5.5</v>
       </c>
       <c r="D278">
-        <v>2.076670408248901</v>
+        <v>2.297951459884644</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5507,7 +5507,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D279">
-        <v>2.870692491531372</v>
+        <v>4.185680866241455</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5521,7 +5521,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D280">
-        <v>14.52227020263672</v>
+        <v>13.56275272369385</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5535,7 +5535,7 @@
         <v>19</v>
       </c>
       <c r="D281">
-        <v>14.31705474853516</v>
+        <v>16.0260009765625</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5549,7 +5549,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D282">
-        <v>2.09925365447998</v>
+        <v>2.223446607589722</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5563,7 +5563,7 @@
         <v>2.5</v>
       </c>
       <c r="D283">
-        <v>2.164671421051025</v>
+        <v>2.293820858001709</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5577,7 +5577,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D284">
-        <v>2.186026573181152</v>
+        <v>2.511190414428711</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5591,7 +5591,7 @@
         <v>7</v>
       </c>
       <c r="D285">
-        <v>4.383175373077393</v>
+        <v>8.188562393188477</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5605,7 +5605,7 @@
         <v>16.79999923706055</v>
       </c>
       <c r="D286">
-        <v>10.96377468109131</v>
+        <v>7.519482135772705</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5619,7 +5619,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D287">
-        <v>2.167108535766602</v>
+        <v>2.202182769775391</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5633,7 +5633,7 @@
         <v>10.19999980926514</v>
       </c>
       <c r="D288">
-        <v>3.898271560668945</v>
+        <v>7.952086448669434</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5647,7 +5647,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D289">
-        <v>9.825247764587402</v>
+        <v>13.21677684783936</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5661,7 +5661,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D290">
-        <v>2.889275550842285</v>
+        <v>3.41517972946167</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5675,7 +5675,7 @@
         <v>27.39999961853027</v>
       </c>
       <c r="D291">
-        <v>17.59992408752441</v>
+        <v>20.69185829162598</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5689,7 +5689,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D292">
-        <v>4.746411323547363</v>
+        <v>3.107666492462158</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5703,7 +5703,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D293">
-        <v>2.133037567138672</v>
+        <v>2.291660785675049</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5717,7 +5717,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D294">
-        <v>2.101354122161865</v>
+        <v>6.308171272277832</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5731,7 +5731,7 @@
         <v>4</v>
       </c>
       <c r="D295">
-        <v>8.56663990020752</v>
+        <v>10.64609622955322</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5745,7 +5745,7 @@
         <v>16.60000038146973</v>
       </c>
       <c r="D296">
-        <v>14.16750240325928</v>
+        <v>18.43309783935547</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5759,7 +5759,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D297">
-        <v>2.33027720451355</v>
+        <v>5.622519493103027</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5773,7 +5773,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D298">
-        <v>2.384620666503906</v>
+        <v>4.79399585723877</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5787,7 +5787,7 @@
         <v>20</v>
       </c>
       <c r="D299">
-        <v>15.01920413970947</v>
+        <v>16.28324317932129</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5801,7 +5801,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D300">
-        <v>10.41736698150635</v>
+        <v>11.58648777008057</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5815,7 +5815,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D301">
-        <v>2.15644359588623</v>
+        <v>2.750494480133057</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5829,7 +5829,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D302">
-        <v>2.391569137573242</v>
+        <v>2.556247711181641</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5843,7 +5843,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D303">
-        <v>3.77056360244751</v>
+        <v>2.255214691162109</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5857,7 +5857,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D304">
-        <v>2.110248565673828</v>
+        <v>2.151130199432373</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5871,7 +5871,7 @@
         <v>22.89999961853027</v>
       </c>
       <c r="D305">
-        <v>8.58458137512207</v>
+        <v>7.510513305664062</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5885,7 +5885,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D306">
-        <v>2.06446361541748</v>
+        <v>5.071527004241943</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5899,7 +5899,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D307">
-        <v>6.005966186523438</v>
+        <v>8.081564903259277</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5913,7 +5913,7 @@
         <v>3</v>
       </c>
       <c r="D308">
-        <v>2.178562879562378</v>
+        <v>2.153831958770752</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5927,7 +5927,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D309">
-        <v>3.750654220581055</v>
+        <v>2.370850563049316</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5941,7 +5941,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D310">
-        <v>2.187371253967285</v>
+        <v>3.723838329315186</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5955,7 +5955,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D311">
-        <v>2.182270050048828</v>
+        <v>2.644569396972656</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5969,7 +5969,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D312">
-        <v>2.803024053573608</v>
+        <v>3.607873916625977</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5983,7 +5983,7 @@
         <v>18</v>
       </c>
       <c r="D313">
-        <v>13.63851261138916</v>
+        <v>15.30198192596436</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5997,7 +5997,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D314">
-        <v>2.143614768981934</v>
+        <v>3.774380207061768</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -6011,7 +6011,7 @@
         <v>1.5</v>
       </c>
       <c r="D315">
-        <v>2.692023754119873</v>
+        <v>5.109992027282715</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -6025,7 +6025,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D316">
-        <v>2.887528419494629</v>
+        <v>8.768840789794922</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -6039,7 +6039,7 @@
         <v>33.90000152587891</v>
       </c>
       <c r="D317">
-        <v>20.29976081848145</v>
+        <v>25.82662010192871</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -6053,7 +6053,7 @@
         <v>19.89999961853027</v>
       </c>
       <c r="D318">
-        <v>13.87343215942383</v>
+        <v>14.54048442840576</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -6067,7 +6067,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D319">
-        <v>6.462191581726074</v>
+        <v>6.123939514160156</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -6081,7 +6081,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D320">
-        <v>3.694844722747803</v>
+        <v>5.168920516967773</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -6095,7 +6095,7 @@
         <v>0.5</v>
       </c>
       <c r="D321">
-        <v>2.176657915115356</v>
+        <v>2.268033504486084</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -6109,7 +6109,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D322">
-        <v>7.972177505493164</v>
+        <v>12.83414745330811</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -6123,7 +6123,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D323">
-        <v>2.098182678222656</v>
+        <v>2.211789608001709</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -6137,7 +6137,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D324">
-        <v>4.446362495422363</v>
+        <v>10.22373676300049</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -6151,7 +6151,7 @@
         <v>8.5</v>
       </c>
       <c r="D325">
-        <v>2.370819568634033</v>
+        <v>2.84186577796936</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -6165,7 +6165,7 @@
         <v>24.79999923706055</v>
       </c>
       <c r="D326">
-        <v>21.05581665039062</v>
+        <v>25.7968578338623</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -6179,7 +6179,7 @@
         <v>11</v>
       </c>
       <c r="D327">
-        <v>4.591669082641602</v>
+        <v>6.979161262512207</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6193,7 +6193,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D328">
-        <v>5.19037389755249</v>
+        <v>3.979213237762451</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -6207,7 +6207,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D329">
-        <v>2.884023666381836</v>
+        <v>3.484338283538818</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6221,7 +6221,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D330">
-        <v>3.940321445465088</v>
+        <v>7.125855445861816</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6235,7 +6235,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D331">
-        <v>2.53426456451416</v>
+        <v>3.094612598419189</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6249,7 +6249,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D332">
-        <v>2.520132780075073</v>
+        <v>5.51685619354248</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6263,7 +6263,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D333">
-        <v>2.214832067489624</v>
+        <v>2.515449285507202</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6277,7 +6277,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D334">
-        <v>2.159763336181641</v>
+        <v>2.08713173866272</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -6291,7 +6291,7 @@
         <v>30.60000038146973</v>
       </c>
       <c r="D335">
-        <v>17.82807922363281</v>
+        <v>25.25528144836426</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -6305,7 +6305,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D336">
-        <v>4.327184200286865</v>
+        <v>3.931141376495361</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -6319,7 +6319,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D337">
-        <v>5.905544281005859</v>
+        <v>7.98498010635376</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6333,7 +6333,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D338">
-        <v>2.17153263092041</v>
+        <v>2.835326194763184</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6347,7 +6347,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D339">
-        <v>2.44414234161377</v>
+        <v>4.71227502822876</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6361,7 +6361,7 @@
         <v>13.19999980926514</v>
       </c>
       <c r="D340">
-        <v>7.528315544128418</v>
+        <v>9.869474411010742</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6375,7 +6375,7 @@
         <v>24.20000076293945</v>
       </c>
       <c r="D341">
-        <v>30.35652160644531</v>
+        <v>22.33916664123535</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6389,7 +6389,7 @@
         <v>12.5</v>
       </c>
       <c r="D342">
-        <v>8.934196472167969</v>
+        <v>9.183741569519043</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6403,7 +6403,7 @@
         <v>34.5</v>
       </c>
       <c r="D343">
-        <v>17.44764137268066</v>
+        <v>21.19674491882324</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6417,7 +6417,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D344">
-        <v>2.146807670593262</v>
+        <v>2.971410274505615</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6431,7 +6431,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D345">
-        <v>2.116568088531494</v>
+        <v>5.36886739730835</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6445,7 +6445,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D346">
-        <v>2.203231573104858</v>
+        <v>5.95082950592041</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6459,7 +6459,7 @@
         <v>2.5</v>
       </c>
       <c r="D347">
-        <v>2.293528079986572</v>
+        <v>4.739973068237305</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6473,7 +6473,7 @@
         <v>22.60000038146973</v>
       </c>
       <c r="D348">
-        <v>15.58875560760498</v>
+        <v>17.66302299499512</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6487,7 +6487,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D349">
-        <v>2.183581352233887</v>
+        <v>2.216366291046143</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6501,7 +6501,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D350">
-        <v>2.270683526992798</v>
+        <v>2.86644983291626</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6515,7 +6515,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D351">
-        <v>2.163383483886719</v>
+        <v>2.239472389221191</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6529,7 +6529,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D352">
-        <v>6.202144145965576</v>
+        <v>7.911834716796875</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6543,7 +6543,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D353">
-        <v>2.118119716644287</v>
+        <v>2.200198173522949</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6557,7 +6557,7 @@
         <v>18.5</v>
       </c>
       <c r="D354">
-        <v>14.1245813369751</v>
+        <v>16.72085762023926</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6571,7 +6571,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D355">
-        <v>4.437142372131348</v>
+        <v>6.292696952819824</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6585,7 +6585,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D356">
-        <v>2.180055618286133</v>
+        <v>2.861404895782471</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6599,7 +6599,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D357">
-        <v>3.905932426452637</v>
+        <v>5.356517314910889</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6613,7 +6613,7 @@
         <v>15.10000038146973</v>
       </c>
       <c r="D358">
-        <v>9.475574493408203</v>
+        <v>9.620053291320801</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6627,7 +6627,7 @@
         <v>19.5</v>
       </c>
       <c r="D359">
-        <v>13.11369132995605</v>
+        <v>15.70265960693359</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6641,7 +6641,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D360">
-        <v>2.204720258712769</v>
+        <v>2.567523956298828</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6655,7 +6655,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D361">
-        <v>2.235718727111816</v>
+        <v>2.09485912322998</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6669,7 +6669,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D362">
-        <v>2.55419921875</v>
+        <v>3.66896915435791</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6683,7 +6683,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D363">
-        <v>5.050123691558838</v>
+        <v>6.064888954162598</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6697,7 +6697,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D364">
-        <v>5.590014457702637</v>
+        <v>4.436554431915283</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6711,7 +6711,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D365">
-        <v>4.719357013702393</v>
+        <v>5.898223876953125</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6725,7 +6725,7 @@
         <v>18.79999923706055</v>
       </c>
       <c r="D366">
-        <v>8.095538139343262</v>
+        <v>14.77715682983398</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6739,7 +6739,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D367">
-        <v>2.205408811569214</v>
+        <v>2.406189203262329</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6753,7 +6753,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D368">
-        <v>3.423717021942139</v>
+        <v>4.490247249603271</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6767,7 +6767,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D369">
-        <v>9.981687545776367</v>
+        <v>9.789376258850098</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6781,7 +6781,7 @@
         <v>30.79999923706055</v>
       </c>
       <c r="D370">
-        <v>19.20845603942871</v>
+        <v>21.04018211364746</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6795,7 +6795,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D371">
-        <v>3.844692230224609</v>
+        <v>4.29931640625</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6809,7 +6809,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D372">
-        <v>4.546978950500488</v>
+        <v>5.824634552001953</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6823,7 +6823,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D373">
-        <v>2.896543979644775</v>
+        <v>7.500885009765625</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6837,7 +6837,7 @@
         <v>4.5</v>
       </c>
       <c r="D374">
-        <v>6.336939811706543</v>
+        <v>15.5467004776001</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6851,7 +6851,7 @@
         <v>2.5</v>
       </c>
       <c r="D375">
-        <v>9.576654434204102</v>
+        <v>16.30147743225098</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6865,7 +6865,7 @@
         <v>31</v>
       </c>
       <c r="D376">
-        <v>12.84823226928711</v>
+        <v>24.36291313171387</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6879,7 +6879,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D377">
-        <v>2.096838474273682</v>
+        <v>2.203946113586426</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="D378">
-        <v>2.228179931640625</v>
+        <v>2.076178073883057</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6907,7 +6907,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D379">
-        <v>2.168030977249146</v>
+        <v>2.91075325012207</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6921,7 +6921,7 @@
         <v>5</v>
       </c>
       <c r="D380">
-        <v>4.104145526885986</v>
+        <v>8.849345207214355</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6935,7 +6935,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D381">
-        <v>2.969385147094727</v>
+        <v>2.529544830322266</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6949,7 +6949,7 @@
         <v>10.10000038146973</v>
       </c>
       <c r="D382">
-        <v>7.796882629394531</v>
+        <v>9.449512481689453</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6963,7 +6963,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D383">
-        <v>5.091714859008789</v>
+        <v>5.708304405212402</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6977,7 +6977,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D384">
-        <v>10.97171020507812</v>
+        <v>16.22121810913086</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6991,7 +6991,7 @@
         <v>30.89999961853027</v>
       </c>
       <c r="D385">
-        <v>15.79962348937988</v>
+        <v>24.70044136047363</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -7005,7 +7005,7 @@
         <v>3</v>
       </c>
       <c r="D386">
-        <v>2.244366645812988</v>
+        <v>2.457477569580078</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -7019,7 +7019,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D387">
-        <v>4.446060657501221</v>
+        <v>5.166165351867676</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -7033,7 +7033,7 @@
         <v>6</v>
       </c>
       <c r="D388">
-        <v>3.694276332855225</v>
+        <v>2.276904582977295</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -7047,7 +7047,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D389">
-        <v>4.948712348937988</v>
+        <v>5.204690456390381</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -7061,7 +7061,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D390">
-        <v>3.210298538208008</v>
+        <v>5.129867553710938</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -7075,7 +7075,7 @@
         <v>3</v>
       </c>
       <c r="D391">
-        <v>6.614753246307373</v>
+        <v>9.019747734069824</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -7089,7 +7089,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D392">
-        <v>2.828978061676025</v>
+        <v>5.045451641082764</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -7103,7 +7103,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D393">
-        <v>2.129552364349365</v>
+        <v>2.858079671859741</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -7117,7 +7117,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D394">
-        <v>3.63291072845459</v>
+        <v>2.630350112915039</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -7131,7 +7131,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D395">
-        <v>4.589639186859131</v>
+        <v>4.605520248413086</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -7145,7 +7145,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D396">
-        <v>3.950253009796143</v>
+        <v>5.55235481262207</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -7159,7 +7159,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D397">
-        <v>4.267269134521484</v>
+        <v>7.157445907592773</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -7173,7 +7173,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D398">
-        <v>3.169144153594971</v>
+        <v>4.193689346313477</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -7187,7 +7187,7 @@
         <v>16.20000076293945</v>
       </c>
       <c r="D399">
-        <v>10.02390480041504</v>
+        <v>13.64245891571045</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7201,7 +7201,7 @@
         <v>8</v>
       </c>
       <c r="D400">
-        <v>2.128585577011108</v>
+        <v>2.256086349487305</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7215,7 +7215,7 @@
         <v>11</v>
       </c>
       <c r="D401">
-        <v>5.59400463104248</v>
+        <v>8.224021911621094</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -7229,7 +7229,7 @@
         <v>13.60000038146973</v>
       </c>
       <c r="D402">
-        <v>4.055468559265137</v>
+        <v>5.714934825897217</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7243,7 +7243,7 @@
         <v>22.79999923706055</v>
       </c>
       <c r="D403">
-        <v>15.45007133483887</v>
+        <v>19.58294486999512</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7257,7 +7257,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D404">
-        <v>2.109432220458984</v>
+        <v>2.473177433013916</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -7271,7 +7271,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D405">
-        <v>2.560801982879639</v>
+        <v>9.598385810852051</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7285,7 +7285,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D406">
-        <v>5.36438512802124</v>
+        <v>7.057150840759277</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7299,7 +7299,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D407">
-        <v>7.654018402099609</v>
+        <v>10.34756755828857</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7313,7 +7313,7 @@
         <v>2</v>
       </c>
       <c r="D408">
-        <v>2.165042400360107</v>
+        <v>3.99565601348877</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7327,7 +7327,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D409">
-        <v>2.153560638427734</v>
+        <v>2.06896185874939</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7341,7 +7341,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D410">
-        <v>2.200487613677979</v>
+        <v>2.069127798080444</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7355,7 +7355,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D411">
-        <v>2.140284299850464</v>
+        <v>2.636745929718018</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -7369,7 +7369,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D412">
-        <v>2.194504976272583</v>
+        <v>4.406561851501465</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -7383,7 +7383,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D413">
-        <v>3.334170818328857</v>
+        <v>2.429029941558838</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7397,7 +7397,7 @@
         <v>14.60000038146973</v>
       </c>
       <c r="D414">
-        <v>12.77237701416016</v>
+        <v>14.79188632965088</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7411,7 +7411,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D415">
-        <v>2.148438930511475</v>
+        <v>2.282428741455078</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7425,7 +7425,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D416">
-        <v>2.098082542419434</v>
+        <v>2.061237812042236</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7439,7 +7439,7 @@
         <v>9</v>
       </c>
       <c r="D417">
-        <v>5.002161979675293</v>
+        <v>3.522013664245605</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7453,7 +7453,7 @@
         <v>32.20000076293945</v>
       </c>
       <c r="D418">
-        <v>30.03564834594727</v>
+        <v>30.2830924987793</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7467,7 +7467,7 @@
         <v>21.29999923706055</v>
       </c>
       <c r="D419">
-        <v>15.63601875305176</v>
+        <v>17.21657752990723</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7481,7 +7481,7 @@
         <v>2</v>
       </c>
       <c r="D420">
-        <v>4.205376148223877</v>
+        <v>3.091567993164062</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7495,7 +7495,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D421">
-        <v>3.393178939819336</v>
+        <v>5.065046787261963</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7509,7 +7509,7 @@
         <v>18.20000076293945</v>
       </c>
       <c r="D422">
-        <v>9.63587760925293</v>
+        <v>11.66814708709717</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7523,7 +7523,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D423">
-        <v>2.186814069747925</v>
+        <v>2.065556287765503</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7537,7 +7537,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D424">
-        <v>5.027762413024902</v>
+        <v>2.261377811431885</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7551,7 +7551,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D425">
-        <v>4.114645481109619</v>
+        <v>2.39886999130249</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7565,7 +7565,7 @@
         <v>30.29999923706055</v>
       </c>
       <c r="D426">
-        <v>16.26878929138184</v>
+        <v>25.98319816589355</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7579,7 +7579,7 @@
         <v>16</v>
       </c>
       <c r="D427">
-        <v>10.2570686340332</v>
+        <v>12.58921051025391</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7593,7 +7593,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D428">
-        <v>2.207826137542725</v>
+        <v>2.074079275131226</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7607,7 +7607,7 @@
         <v>14.30000019073486</v>
       </c>
       <c r="D429">
-        <v>9.47810173034668</v>
+        <v>5.215440273284912</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7621,7 +7621,7 @@
         <v>11.5</v>
       </c>
       <c r="D430">
-        <v>6.619384765625</v>
+        <v>4.542900562286377</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7635,7 +7635,7 @@
         <v>2.5</v>
       </c>
       <c r="D431">
-        <v>2.145450830459595</v>
+        <v>2.343001842498779</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7649,7 +7649,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D432">
-        <v>2.123615980148315</v>
+        <v>2.34141731262207</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7663,7 +7663,7 @@
         <v>4</v>
       </c>
       <c r="D433">
-        <v>4.15284538269043</v>
+        <v>2.432904243469238</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7677,7 +7677,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D434">
-        <v>2.173889398574829</v>
+        <v>2.974737405776978</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7691,7 +7691,7 @@
         <v>1</v>
       </c>
       <c r="D435">
-        <v>2.224950075149536</v>
+        <v>2.114330291748047</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7705,7 +7705,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D436">
-        <v>2.20558500289917</v>
+        <v>2.23570728302002</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7719,7 +7719,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D437">
-        <v>2.146239519119263</v>
+        <v>2.071221828460693</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7733,7 +7733,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D438">
-        <v>2.175229072570801</v>
+        <v>2.167539119720459</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7747,7 +7747,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D439">
-        <v>2.108402490615845</v>
+        <v>5.465659141540527</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7761,7 +7761,7 @@
         <v>2</v>
       </c>
       <c r="D440">
-        <v>2.222394227981567</v>
+        <v>2.117420196533203</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7775,7 +7775,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D441">
-        <v>2.096222639083862</v>
+        <v>3.096199512481689</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7789,7 +7789,7 @@
         <v>1</v>
       </c>
       <c r="D442">
-        <v>2.140038728713989</v>
+        <v>2.54278564453125</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7803,7 +7803,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D443">
-        <v>3.366540193557739</v>
+        <v>9.444920539855957</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7817,7 +7817,7 @@
         <v>20.70000076293945</v>
       </c>
       <c r="D444">
-        <v>18.41808891296387</v>
+        <v>21.41324424743652</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7831,7 +7831,7 @@
         <v>16.10000038146973</v>
       </c>
       <c r="D445">
-        <v>7.41472053527832</v>
+        <v>14.12966632843018</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7845,7 +7845,7 @@
         <v>4</v>
       </c>
       <c r="D446">
-        <v>3.153689384460449</v>
+        <v>2.319824695587158</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7859,7 +7859,7 @@
         <v>34.79999923706055</v>
       </c>
       <c r="D447">
-        <v>15.59451484680176</v>
+        <v>17.15317153930664</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7873,7 +7873,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D448">
-        <v>2.203685283660889</v>
+        <v>2.50332498550415</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -7887,7 +7887,7 @@
         <v>10.30000019073486</v>
       </c>
       <c r="D449">
-        <v>6.923272609710693</v>
+        <v>5.466609954833984</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -7901,7 +7901,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D450">
-        <v>2.148790597915649</v>
+        <v>2.222799777984619</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -7915,7 +7915,7 @@
         <v>16.10000038146973</v>
       </c>
       <c r="D451">
-        <v>16.20952033996582</v>
+        <v>16.72642517089844</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -7929,7 +7929,7 @@
         <v>4</v>
       </c>
       <c r="D452">
-        <v>2.236437559127808</v>
+        <v>2.667558908462524</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -7943,7 +7943,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D453">
-        <v>2.212753772735596</v>
+        <v>5.407693386077881</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -7957,7 +7957,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D454">
-        <v>2.234161615371704</v>
+        <v>2.03250789642334</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -7971,7 +7971,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D455">
-        <v>4.804680347442627</v>
+        <v>5.971662044525146</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -7985,7 +7985,7 @@
         <v>33.5</v>
       </c>
       <c r="D456">
-        <v>19.92923545837402</v>
+        <v>25.75099563598633</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -7999,7 +7999,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D457">
-        <v>2.174455642700195</v>
+        <v>2.479958057403564</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -8013,7 +8013,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D458">
-        <v>3.623273372650146</v>
+        <v>2.933723449707031</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -8027,7 +8027,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D459">
-        <v>3.470847129821777</v>
+        <v>2.298211812973022</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -8041,7 +8041,7 @@
         <v>5</v>
       </c>
       <c r="D460">
-        <v>4.149365901947021</v>
+        <v>5.627962112426758</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -8055,7 +8055,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D461">
-        <v>2.178525447845459</v>
+        <v>3.729063034057617</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -8069,7 +8069,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D462">
-        <v>2.27935266494751</v>
+        <v>2.495477676391602</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -8083,7 +8083,7 @@
         <v>2</v>
       </c>
       <c r="D463">
-        <v>2.157467126846313</v>
+        <v>2.146000385284424</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -8097,7 +8097,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D464">
-        <v>2.211428880691528</v>
+        <v>2.296573877334595</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -8111,7 +8111,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D465">
-        <v>11.66586303710938</v>
+        <v>6.840096950531006</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -8125,7 +8125,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D466">
-        <v>2.155966758728027</v>
+        <v>2.325632095336914</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -8139,7 +8139,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D467">
-        <v>2.158326148986816</v>
+        <v>3.699888706207275</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -8153,7 +8153,7 @@
         <v>6.5</v>
       </c>
       <c r="D468">
-        <v>5.450505256652832</v>
+        <v>5.315851211547852</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -8167,7 +8167,7 @@
         <v>14</v>
       </c>
       <c r="D469">
-        <v>4.902934551239014</v>
+        <v>3.27272891998291</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -8181,7 +8181,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D470">
-        <v>2.871614456176758</v>
+        <v>3.645992755889893</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -8195,7 +8195,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D471">
-        <v>2.820488452911377</v>
+        <v>8.313342094421387</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -8209,7 +8209,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D472">
-        <v>5.59276294708252</v>
+        <v>2.497401237487793</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -8223,7 +8223,7 @@
         <v>0.5</v>
       </c>
       <c r="D473">
-        <v>2.15774941444397</v>
+        <v>4.265759944915771</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -8237,7 +8237,7 @@
         <v>5.5</v>
       </c>
       <c r="D474">
-        <v>6.24903392791748</v>
+        <v>8.192357063293457</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -8251,7 +8251,7 @@
         <v>22.60000038146973</v>
       </c>
       <c r="D475">
-        <v>12.60960006713867</v>
+        <v>15.33060550689697</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -8265,7 +8265,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D476">
-        <v>7.816338539123535</v>
+        <v>10.05625534057617</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -8279,7 +8279,7 @@
         <v>8.5</v>
       </c>
       <c r="D477">
-        <v>6.001059532165527</v>
+        <v>6.278114318847656</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -8293,7 +8293,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D478">
-        <v>2.067239046096802</v>
+        <v>2.13270378112793</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -8307,7 +8307,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D479">
-        <v>4.969878196716309</v>
+        <v>2.508024215698242</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -8321,7 +8321,7 @@
         <v>5</v>
       </c>
       <c r="D480">
-        <v>2.086077928543091</v>
+        <v>2.19121789932251</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8335,7 +8335,7 @@
         <v>1.5</v>
       </c>
       <c r="D481">
-        <v>2.186635971069336</v>
+        <v>2.177352905273438</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -8349,7 +8349,7 @@
         <v>6.5</v>
       </c>
       <c r="D482">
-        <v>5.523959159851074</v>
+        <v>7.030422210693359</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -8363,7 +8363,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D483">
-        <v>2.143458366394043</v>
+        <v>2.54536771774292</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -8377,7 +8377,7 @@
         <v>0.5</v>
       </c>
       <c r="D484">
-        <v>2.342397928237915</v>
+        <v>4.571662425994873</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8391,7 +8391,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D485">
-        <v>2.071502447128296</v>
+        <v>2.6184401512146</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8405,7 +8405,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D486">
-        <v>2.070607662200928</v>
+        <v>2.449565410614014</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8419,7 +8419,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D487">
-        <v>9.548904418945312</v>
+        <v>10.56495571136475</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8433,7 +8433,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D488">
-        <v>8.146138191223145</v>
+        <v>8.356043815612793</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8447,7 +8447,7 @@
         <v>7</v>
       </c>
       <c r="D489">
-        <v>2.656467437744141</v>
+        <v>2.51489782333374</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8461,7 +8461,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D490">
-        <v>4.65171480178833</v>
+        <v>6.668456554412842</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8475,7 +8475,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D491">
-        <v>4.025985240936279</v>
+        <v>7.324432373046875</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8489,7 +8489,7 @@
         <v>5.5</v>
       </c>
       <c r="D492">
-        <v>2.136335134506226</v>
+        <v>2.564064502716064</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8503,7 +8503,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D493">
-        <v>2.202750444412231</v>
+        <v>2.306819915771484</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -8517,7 +8517,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D494">
-        <v>2.177042484283447</v>
+        <v>4.543416500091553</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8531,7 +8531,7 @@
         <v>1</v>
       </c>
       <c r="D495">
-        <v>2.196231603622437</v>
+        <v>2.299681901931763</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8545,7 +8545,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D496">
-        <v>2.08889627456665</v>
+        <v>4.60887622833252</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8559,7 +8559,7 @@
         <v>14.30000019073486</v>
       </c>
       <c r="D497">
-        <v>3.943724155426025</v>
+        <v>6.748816013336182</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8573,7 +8573,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D498">
-        <v>2.196112632751465</v>
+        <v>6.287200450897217</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8587,7 +8587,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D499">
-        <v>2.121936559677124</v>
+        <v>4.409556865692139</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8601,7 +8601,7 @@
         <v>3.5</v>
       </c>
       <c r="D500">
-        <v>3.780651092529297</v>
+        <v>3.24192476272583</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8615,7 +8615,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D501">
-        <v>7.764363288879395</v>
+        <v>7.841191291809082</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8629,7 +8629,7 @@
         <v>10.5</v>
       </c>
       <c r="D502">
-        <v>5.386960029602051</v>
+        <v>7.941720962524414</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -8643,7 +8643,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D503">
-        <v>7.089581966400146</v>
+        <v>7.205958366394043</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -8657,7 +8657,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D504">
-        <v>2.180804252624512</v>
+        <v>2.440875291824341</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -8671,7 +8671,7 @@
         <v>10.60000038146973</v>
       </c>
       <c r="D505">
-        <v>5.020886421203613</v>
+        <v>10.00203037261963</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -8685,7 +8685,7 @@
         <v>22</v>
       </c>
       <c r="D506">
-        <v>16.92346382141113</v>
+        <v>22.93536567687988</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -8699,7 +8699,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D507">
-        <v>2.154317617416382</v>
+        <v>3.36896800994873</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -8713,7 +8713,7 @@
         <v>4.5</v>
       </c>
       <c r="D508">
-        <v>3.91392993927002</v>
+        <v>2.55265998840332</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -8727,7 +8727,7 @@
         <v>5.5</v>
       </c>
       <c r="D509">
-        <v>2.102035045623779</v>
+        <v>2.429812431335449</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -8741,7 +8741,7 @@
         <v>6.5</v>
       </c>
       <c r="D510">
-        <v>11.61677265167236</v>
+        <v>14.9190149307251</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -8755,7 +8755,7 @@
         <v>1</v>
       </c>
       <c r="D511">
-        <v>2.160244941711426</v>
+        <v>2.071508407592773</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -8769,7 +8769,7 @@
         <v>14.39999961853027</v>
       </c>
       <c r="D512">
-        <v>10.06745624542236</v>
+        <v>13.67177486419678</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -8783,7 +8783,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D513">
-        <v>2.165971517562866</v>
+        <v>2.164651393890381</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -8797,7 +8797,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D514">
-        <v>2.508326530456543</v>
+        <v>3.764042854309082</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -8811,7 +8811,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D515">
-        <v>2.231007099151611</v>
+        <v>2.258634090423584</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -8825,7 +8825,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D516">
-        <v>2.079771995544434</v>
+        <v>3.707036972045898</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -8839,7 +8839,7 @@
         <v>25.60000038146973</v>
       </c>
       <c r="D517">
-        <v>8.643710136413574</v>
+        <v>9.953230857849121</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -8853,7 +8853,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D518">
-        <v>6.520968437194824</v>
+        <v>10.59896755218506</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -8867,7 +8867,7 @@
         <v>3.5</v>
       </c>
       <c r="D519">
-        <v>2.235126495361328</v>
+        <v>2.04623556137085</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -8881,7 +8881,7 @@
         <v>4.5</v>
       </c>
       <c r="D520">
-        <v>8.110356330871582</v>
+        <v>12.75152206420898</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -8895,7 +8895,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D521">
-        <v>8.04352855682373</v>
+        <v>11.11701107025146</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -8909,7 +8909,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D522">
-        <v>3.681330680847168</v>
+        <v>7.931002616882324</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -8923,7 +8923,7 @@
         <v>13.39999961853027</v>
       </c>
       <c r="D523">
-        <v>8.497552871704102</v>
+        <v>7.380884170532227</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -8937,7 +8937,7 @@
         <v>24.79999923706055</v>
       </c>
       <c r="D524">
-        <v>10.07580947875977</v>
+        <v>15.89259815216064</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -8951,7 +8951,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D525">
-        <v>6.621335029602051</v>
+        <v>9.727639198303223</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -8965,7 +8965,7 @@
         <v>16.79999923706055</v>
       </c>
       <c r="D526">
-        <v>13.26535987854004</v>
+        <v>16.41022872924805</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -8979,7 +8979,7 @@
         <v>4</v>
       </c>
       <c r="D527">
-        <v>2.157576560974121</v>
+        <v>2.24016809463501</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -8993,7 +8993,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D528">
-        <v>4.245228290557861</v>
+        <v>5.018046855926514</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -9007,7 +9007,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D529">
-        <v>2.16133451461792</v>
+        <v>2.335494995117188</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -9021,7 +9021,7 @@
         <v>33.29999923706055</v>
       </c>
       <c r="D530">
-        <v>19.5252513885498</v>
+        <v>22.94772911071777</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9035,7 +9035,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D531">
-        <v>2.709129810333252</v>
+        <v>6.119382381439209</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -9049,7 +9049,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D532">
-        <v>4.686598300933838</v>
+        <v>9.695350646972656</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -9063,7 +9063,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D533">
-        <v>13.23366355895996</v>
+        <v>13.81974124908447</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -9077,7 +9077,7 @@
         <v>23.10000038146973</v>
       </c>
       <c r="D534">
-        <v>17.24422073364258</v>
+        <v>18.8831729888916</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9091,7 +9091,7 @@
         <v>13.89999961853027</v>
       </c>
       <c r="D535">
-        <v>7.250302314758301</v>
+        <v>10.10581684112549</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -9105,7 +9105,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D536">
-        <v>2.240557193756104</v>
+        <v>2.048460483551025</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -9119,7 +9119,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D537">
-        <v>5.423793315887451</v>
+        <v>9.354578971862793</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -9133,7 +9133,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D538">
-        <v>2.146022319793701</v>
+        <v>3.391711711883545</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -9147,7 +9147,7 @@
         <v>11.5</v>
       </c>
       <c r="D539">
-        <v>4.340306758880615</v>
+        <v>6.47726583480835</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -9161,7 +9161,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D540">
-        <v>2.97895622253418</v>
+        <v>8.017860412597656</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9175,7 +9175,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D541">
-        <v>2.104836940765381</v>
+        <v>2.667377471923828</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -9189,7 +9189,7 @@
         <v>55.20000076293945</v>
       </c>
       <c r="D542">
-        <v>32.69988632202148</v>
+        <v>46.31887435913086</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9203,7 +9203,7 @@
         <v>16.20000076293945</v>
       </c>
       <c r="D543">
-        <v>8.996950149536133</v>
+        <v>10.32927799224854</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9217,7 +9217,7 @@
         <v>8</v>
       </c>
       <c r="D544">
-        <v>2.351079940795898</v>
+        <v>3.302892208099365</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9231,7 +9231,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D545">
-        <v>9.221531867980957</v>
+        <v>7.923203945159912</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -9245,7 +9245,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D546">
-        <v>2.177987575531006</v>
+        <v>3.094663619995117</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9259,7 +9259,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D547">
-        <v>5.592860221862793</v>
+        <v>6.645188331604004</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9273,7 +9273,7 @@
         <v>16.39999961853027</v>
       </c>
       <c r="D548">
-        <v>6.474989891052246</v>
+        <v>9.096325874328613</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -9287,7 +9287,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D549">
-        <v>4.004830360412598</v>
+        <v>5.222394943237305</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9301,7 +9301,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D550">
-        <v>8.881759643554688</v>
+        <v>10.20814800262451</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9315,7 +9315,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D551">
-        <v>2.156569957733154</v>
+        <v>2.565593481063843</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -9329,7 +9329,7 @@
         <v>7</v>
       </c>
       <c r="D552">
-        <v>4.957324981689453</v>
+        <v>6.2644944190979</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9343,7 +9343,7 @@
         <v>1</v>
       </c>
       <c r="D553">
-        <v>2.103503227233887</v>
+        <v>2.527657032012939</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -9357,7 +9357,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D554">
-        <v>2.33617091178894</v>
+        <v>7.344226837158203</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -9371,7 +9371,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D555">
-        <v>3.281586408615112</v>
+        <v>3.452158451080322</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -9385,7 +9385,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D556">
-        <v>3.825326442718506</v>
+        <v>3.764064311981201</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9399,7 +9399,7 @@
         <v>5.5</v>
       </c>
       <c r="D557">
-        <v>3.136115074157715</v>
+        <v>4.736855506896973</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -9413,7 +9413,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D558">
-        <v>2.103510618209839</v>
+        <v>5.525269508361816</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -9427,7 +9427,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D559">
-        <v>2.182538032531738</v>
+        <v>2.067689895629883</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -9441,7 +9441,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D560">
-        <v>4.53217887878418</v>
+        <v>5.216500759124756</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -9455,7 +9455,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D561">
-        <v>2.247035026550293</v>
+        <v>2.082593202590942</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -9469,7 +9469,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D562">
-        <v>3.77529239654541</v>
+        <v>2.379213809967041</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -9483,7 +9483,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D563">
-        <v>2.107864379882812</v>
+        <v>2.234625816345215</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -9497,7 +9497,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D564">
-        <v>5.853197574615479</v>
+        <v>4.07571268081665</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -9511,7 +9511,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D565">
-        <v>10.7948055267334</v>
+        <v>6.398872852325439</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -9525,7 +9525,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D566">
-        <v>3.329988479614258</v>
+        <v>3.002296447753906</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -9539,7 +9539,7 @@
         <v>10.60000038146973</v>
       </c>
       <c r="D567">
-        <v>12.5857048034668</v>
+        <v>20.01311683654785</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -9553,7 +9553,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D568">
-        <v>2.118922710418701</v>
+        <v>2.541814804077148</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -9567,7 +9567,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D569">
-        <v>2.044057130813599</v>
+        <v>2.073859453201294</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -9581,7 +9581,7 @@
         <v>16.20000076293945</v>
       </c>
       <c r="D570">
-        <v>13.01965713500977</v>
+        <v>13.05029392242432</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -9595,7 +9595,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D571">
-        <v>2.51708197593689</v>
+        <v>6.172528266906738</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -9609,7 +9609,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D572">
-        <v>2.094403982162476</v>
+        <v>2.336106777191162</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -9623,7 +9623,7 @@
         <v>1</v>
       </c>
       <c r="D573">
-        <v>2.254640817642212</v>
+        <v>2.208226442337036</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -9637,7 +9637,7 @@
         <v>1.5</v>
       </c>
       <c r="D574">
-        <v>2.271086454391479</v>
+        <v>2.053659677505493</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -9651,7 +9651,7 @@
         <v>3.5</v>
       </c>
       <c r="D575">
-        <v>2.11568808555603</v>
+        <v>2.460211277008057</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -9665,7 +9665,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D576">
-        <v>2.057568073272705</v>
+        <v>2.134692192077637</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -9679,7 +9679,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D577">
-        <v>6.038522720336914</v>
+        <v>10.11063003540039</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -9693,7 +9693,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D578">
-        <v>7.610182762145996</v>
+        <v>16.72275161743164</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -9707,7 +9707,7 @@
         <v>23.39999961853027</v>
       </c>
       <c r="D579">
-        <v>15.35169792175293</v>
+        <v>20.09346580505371</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -9721,7 +9721,7 @@
         <v>10</v>
       </c>
       <c r="D580">
-        <v>6.69981861114502</v>
+        <v>6.049842834472656</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -9735,7 +9735,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D581">
-        <v>4.926936149597168</v>
+        <v>2.425769805908203</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -9749,7 +9749,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D582">
-        <v>2.122668743133545</v>
+        <v>2.187040328979492</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -9763,7 +9763,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D583">
-        <v>14.36932563781738</v>
+        <v>21.25346183776855</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -9777,7 +9777,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D584">
-        <v>3.949701309204102</v>
+        <v>2.866353988647461</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -9791,7 +9791,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D585">
-        <v>7.970827579498291</v>
+        <v>7.273097991943359</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -9805,7 +9805,7 @@
         <v>15.19999980926514</v>
       </c>
       <c r="D586">
-        <v>12.04421138763428</v>
+        <v>15.14611434936523</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -9819,7 +9819,7 @@
         <v>0</v>
       </c>
       <c r="D587">
-        <v>2.152937650680542</v>
+        <v>3.04338550567627</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -9833,7 +9833,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D588">
-        <v>2.150146722793579</v>
+        <v>2.65316104888916</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -9847,7 +9847,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D589">
-        <v>5.248739719390869</v>
+        <v>10.54887199401855</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -9861,7 +9861,7 @@
         <v>1</v>
       </c>
       <c r="D590">
-        <v>2.730174541473389</v>
+        <v>2.442696571350098</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -9875,7 +9875,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D591">
-        <v>3.975704193115234</v>
+        <v>3.173203945159912</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -9889,7 +9889,7 @@
         <v>21.10000038146973</v>
       </c>
       <c r="D592">
-        <v>23.52828216552734</v>
+        <v>27.4525089263916</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -9903,7 +9903,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D593">
-        <v>2.135493278503418</v>
+        <v>2.325215339660645</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -9917,7 +9917,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D594">
-        <v>2.137382507324219</v>
+        <v>3.791532516479492</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -9931,7 +9931,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D595">
-        <v>2.152342081069946</v>
+        <v>3.092318534851074</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -9945,7 +9945,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D596">
-        <v>2.122103214263916</v>
+        <v>2.023692846298218</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -9959,7 +9959,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D597">
-        <v>10.29524803161621</v>
+        <v>13.15253734588623</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -9973,7 +9973,7 @@
         <v>2</v>
       </c>
       <c r="D598">
-        <v>2.919047594070435</v>
+        <v>2.321877956390381</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -9987,7 +9987,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D599">
-        <v>2.201515913009644</v>
+        <v>2.283967018127441</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -10001,7 +10001,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D600">
-        <v>5.375001907348633</v>
+        <v>9.088030815124512</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -10015,7 +10015,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D601">
-        <v>2.178410053253174</v>
+        <v>2.251755237579346</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -10029,7 +10029,7 @@
         <v>18.39999961853027</v>
       </c>
       <c r="D602">
-        <v>13.77412033081055</v>
+        <v>7.604987144470215</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -10043,7 +10043,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D603">
-        <v>2.096047639846802</v>
+        <v>6.057903289794922</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -10057,7 +10057,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D604">
-        <v>2.548542022705078</v>
+        <v>2.659281730651855</v>
       </c>
     </row>
   </sheetData>
